--- a/ig/DM-DECEMBRE-2025/ValueSet-JDV-J18-EquipementSpecifique-ROR.xlsx
+++ b/ig/DM-DECEMBRE-2025/ValueSet-JDV-J18-EquipementSpecifique-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="341">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250623120000</t>
+    <t>20251222120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-23T12:00:00+01:00</t>
+    <t>2025-12-22T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1015,6 +1015,18 @@
   </si>
   <si>
     <t>Douche accessible aux personnes en fauteuil roulant</t>
+  </si>
+  <si>
+    <t>234</t>
+  </si>
+  <si>
+    <t>Espace de consommation de drogues injectables</t>
+  </si>
+  <si>
+    <t>235</t>
+  </si>
+  <si>
+    <t>Espace de consommation de drogues à fumer</t>
   </si>
   <si>
     <t/>
@@ -1285,7 +1297,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B156"/>
+  <dimension ref="A1:B158"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -2529,15 +2541,31 @@
         <v>334</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="B157" t="s" s="2">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="B158" t="s" s="2">
+        <v>340</v>
       </c>
     </row>
   </sheetData>
